--- a/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-1 電流的化學效應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下1-1 電流的化學效應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>電流通過電解質引起化學變化稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>電流的化學效應</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>避免重金屬進入環境符合法規</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>效應</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>利用電流在表面鍍金屬是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>電鍍</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>美觀防鏽</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>負極</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>電解質溶液</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>鍍層</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>電鍍需要什麼溶液？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>電解質溶液</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>減少環境汙染</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不能</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>電鍍的目的常是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>待鍍物</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氣體(氫氧)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水源與土壤</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>美觀防鏽</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>硫酸銅廢液含有？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>重金屬(銅)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>氣體(氫氧)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氫與氧</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>汙染</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>重金屬廢液應如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>妥善處理</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>幾乎不能</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>化學效應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>防汙</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>純水能進行電解嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>幾乎不能</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>負極</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>化學效應</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>需電解質</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>電解水會產生？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化學效應</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>美觀防鏽</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>氣體(氫氧)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>分解</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>電解水通電後兩極產生的氣體是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>氫與氧</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>重金屬(銅)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>負極</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>電解</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>電鍍是利用電流的什麼效應？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>電解質溶液</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>化學效應</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>減少環境汙染</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>電解電鍍</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>效應</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-1 電流的化學效應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下1-1 電流的化學效應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>電鍍時待鍍物接哪極？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>待鍍物</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>負極</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>環境與健康</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>陰極</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>電流化學效應的應用有？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>氣體(氫氧)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>美觀防鏽</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>電解電鍍</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>化學效應</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>重金屬汙染會危害？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電解質溶液</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>環境與健康</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>危害</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>為何硫酸銅廢液不可亂倒？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鍍上金屬層既美觀又隔絕空氣水</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>銅離子等重金屬累積危害生物與人體</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>含銅重金屬汙染</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>環保</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>電鍍能防鏽因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>金屬鍍層隔絕</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>重金屬(銅)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>待鍍物</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>電解質在化學效應中作用？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>導電並參與反應</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>減量回收與妥善處理廢液</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>避免重金屬進入環境符合法規</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>電流的化學效應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>關鍵</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>電流通過電解質除導電還引起？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減少環境汙染</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>負極</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>電解質溶液</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>效應</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>處理重金屬廢液的意義？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>減少環境汙染</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>化學效應</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>美觀防鏽</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>妥善處理</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電鍍時金屬鍍在接負極的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>金屬鍍層隔絕</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>待鍍物</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電解電鍍</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>陰極</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>重金屬廢液未處理排放會汙染？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>水源與土壤</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>妥善處理</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>重金屬(銅)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>電鍍</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>汙染</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-1 電流的化學效應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下1-1 電流的化學效應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何電鍍需要用電解質溶液而非純水？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>減量回收與妥善處理廢液</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>電流的化學效應</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>鍍上金屬層既美觀又隔絕空氣水</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>純水幾乎不導電無法傳遞電流進行反應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>討論硫酸銅廢液排放對水體的影響？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>銅離子等重金屬累積危害生物與人體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>減量回收與妥善處理廢液</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>汙染</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>電鍍如何同時達到美觀與防鏽？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>累積(生物累積)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重現象與議題</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>鍍上金屬層既美觀又隔絕空氣水</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>雙效</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>重金屬為何在生物體內特別危險？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重現象與議題</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>不易代謝會累積(生物累積)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>含銅重金屬汙染</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>累積</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>工廠處理電鍍廢液的必要性？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重現象與議題</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不易代謝會累積(生物累積)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>避免重金屬進入環境符合法規</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>責任</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>電流的化學效應與熱效應差別？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>化學效應引起化學變化、熱效應產熱</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>電流的化學效應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何從源頭減少重金屬汙染？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>減量回收與妥善處理廢液</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>化學效應引起化學變化、熱效應產熱</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不易代謝會累積(生物累積)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>策略</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱不涉電鍍反應式？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>避免重金屬進入環境符合法規</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中重現象與議題</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>導電並參與反應</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何純水不易電解需加電解質？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電流的化學效應</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>避免重金屬進入環境符合法規</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>含銅重金屬汙染</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>純水幾乎不導電</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>重金屬會在食物鏈中如何？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>含銅重金屬汙染</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>累積(生物累積)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>鍍上金屬層既美觀又隔絕空氣水</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>累積</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>效應</t>
+          <t>化學效應：電流流過電解質溶液時會引發化學變化，這種現象就叫電流的化學效應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>鍍層</t>
+          <t>鍍層：利用電流通過溶液，使金屬離子附著在物體表面形成一層金屬鍍層，這種技術叫電鍍</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：電鍍必須用能導電的電解質溶液，電流才能通過並讓金屬離子移動附著</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>用途</t>
+          <t>用途：電鍍常是為了讓物品表面更美觀，同時金屬鍍層也能隔絕空氣、防止生鏽</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>汙染</t>
+          <t>汙染：硫酸銅溶液裡含有銅這種重金屬離子，隨意排放會造成環境汙染</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防汙</t>
+          <t>防汙：含重金屬的廢液必須經過妥善處理，才能排放，避免汙染水源與土壤</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>需電解質</t>
+          <t>需電解質：純水裡幾乎沒有帶電的離子，導電能力很差，所以幾乎無法電解</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>分解</t>
+          <t>分解：電解水時水分子會被拆開，在電極上分別產生氫氣和氧氣兩種氣體</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>電解</t>
+          <t>電解：水通電分解後，會在兩個電極分別產生氫氣和氧氣兩種氣體</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>效應</t>
+          <t>效應：電鍍是電流通過電解質溶液引起化學變化，屬於電流的化學效應</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>陰極</t>
+          <t>陰極：要鍍上金屬的物品要接電源的負極，金屬離子才會被吸引過來附著</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：電解和電鍍都是利用電流通過電解質溶液產生化學變化的實際應用</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>危害</t>
+          <t>危害：重金屬一旦汙染環境，會透過水或食物進入生物體，危害環境與人體健康</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>環保</t>
+          <t>環保：硫酸銅廢液裡含有銅這種重金屬，隨意倒掉會汙染水源與土壤</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：電鍍在物品表面形成一層金屬膜，能隔絕空氣和水分，避免物品生鏽</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>關鍵</t>
+          <t>關鍵：電解質溶液裡的離子既能幫助導電，也會參與電極上發生的化學反應</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>效應</t>
+          <t>效應：電流通過電解質溶液時，除了導電之外，還會在電極上引發化學變化</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：把重金屬廢液處理乾淨才排放，可以減少對環境和生態的長期傷害</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>陰極</t>
+          <t>陰極：要鍍上金屬的物品接負極(陰極)，金屬離子才會被吸過來附著上去</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>汙染</t>
+          <t>汙染：含重金屬的廢液如果沒處理就排放，會滲入並汙染水源和土壤</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：純水裡幾乎沒有能移動的離子，電流無法順利通過，也就無法完成電鍍反應</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>汙染</t>
+          <t>汙染：銅離子等重金屬若隨廢液排入水體，會在水中生物體內慢慢累積，最後危害人體健康</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>雙效</t>
+          <t>雙效：在物品表面鍍上一層光亮金屬，既讓外觀變美，又能隔絕空氣與水分防止生鏽</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>累積</t>
+          <t>累積：重金屬很難被生物體分解排出，會一直留在體內慢慢累積，濃度越來越高</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>責任</t>
+          <t>責任：工廠必須處理電鍍廢液才能排放，這樣才不會讓重金屬流入環境，也符合環保法規</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：化學效應是讓電解質溶液產生化學變化，熱效應則是電流通過導體時使溫度升高</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>策略</t>
+          <t>策略：從一開始就減少使用量、回收再利用，並確實處理廢液，能有效減少重金屬汙染</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：詳細的化學反應式留到高中再學，國中階段著重理解電鍍現象與環境議題</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：純水裡幾乎沒有能移動的離子，導電能力很差，加入電解質才能順利通電分解</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>累積</t>
+          <t>累積：重金屬不易被生物代謝排出，會沿著食物鏈一層層往上累積、越來越濃</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-1_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>幾乎不能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氫與氧</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>美觀防鏽</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>負極</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>電解質溶液</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>氣體(氫氧)</t>
+          <t>妥善處理</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>美觀防鏽</t>
+          <t>電解質溶液</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>化學效應</t>
+          <t>水源與土壤</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>減量回收與妥善處理廢液</t>
+          <t>累積(生物累積)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>鍍上金屬層既美觀又隔絕空氣水</t>
+          <t>導電並參與反應</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>移高中,國中重現象與議題</t>
+          <t>導電並參與反應</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>含銅重金屬汙染</t>
+          <t>電流的化學效應</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+          <t>銅離子等重金屬累積危害生物與人體</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>電流的化學效應</t>
+          <t>鍍上金屬層既美觀又隔絕空氣水</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>銅離子等重金屬累積危害生物與人體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>避免重金屬進入環境符合法規</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>含銅重金屬汙染</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>含銅重金屬汙染</t>
+          <t>電流的化學效應</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>純水幾乎不導電無法傳遞電流進行反應</t>
+          <t>導電並參與反應</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>鍍上金屬層既美觀又隔絕空氣水</t>
+          <t>減量回收與妥善處理廢液</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
